--- a/Mina_Stat_Formler/data_pipeline/excel_filer/konkurrenskraft_index.xlsx
+++ b/Mina_Stat_Formler/data_pipeline/excel_filer/konkurrenskraft_index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\OBS\OBS 2026_2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80518884-3AE2-43E7-A62B-806A54E30F77}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFF4356-A907-4EB7-A5E3-C08205EF34EB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17505" xr2:uid="{72CE4493-A20D-4097-9ED9-F03ED7B63204}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Ung_bef" sheetId="17" r:id="rId3"/>
     <sheet name="Sysselsatta" sheetId="3" r:id="rId4"/>
     <sheet name="KIBS" sheetId="4" r:id="rId5"/>
-    <sheet name="Inpendling" sheetId="5" r:id="rId6"/>
+    <sheet name="Inpendling" sheetId="31" r:id="rId6"/>
     <sheet name="Utpendling" sheetId="19" r:id="rId7"/>
     <sheet name="Lång_eftergymnasial_procent" sheetId="6" r:id="rId8"/>
     <sheet name="Lång_eftergymnasial_antal" sheetId="12" r:id="rId9"/>
@@ -5492,11 +5492,11 @@
         <v>36</v>
       </c>
       <c r="B25" s="22">
-        <f t="shared" ref="B25:AA25" si="13">SUM(B14-B5)</f>
+        <f>SUM(B14-B5)</f>
         <v>7293</v>
       </c>
       <c r="C25" s="22">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="C25:AA25" si="13">SUM(C14-C5)</f>
         <v>7525</v>
       </c>
       <c r="D25" s="22">
@@ -7496,11 +7496,11 @@
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
       <c r="D24" s="22">
-        <f t="shared" ref="D24:Z24" si="17">+D5</f>
+        <f>+D5</f>
         <v>667</v>
       </c>
       <c r="E24" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="E24:Z24" si="17">+E5</f>
         <v>686</v>
       </c>
       <c r="F24" s="22">
@@ -7599,11 +7599,11 @@
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
       <c r="D25" s="22">
-        <f t="shared" ref="D25:Z25" si="19">+D4</f>
+        <f>+D4</f>
         <v>761</v>
       </c>
       <c r="E25" s="22">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="E25:Z25" si="19">+E4</f>
         <v>759</v>
       </c>
       <c r="F25" s="22">
@@ -9896,11 +9896,11 @@
         <v>36</v>
       </c>
       <c r="B25" s="22">
-        <f t="shared" ref="B25:Z25" si="19">SUM(B14-B5)</f>
+        <f>SUM(B14-B5)</f>
         <v>7436</v>
       </c>
       <c r="C25" s="22">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="C25:Z25" si="19">SUM(C14-C5)</f>
         <v>7468</v>
       </c>
       <c r="D25" s="22">
@@ -11898,11 +11898,11 @@
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="22">
-        <f t="shared" ref="D24:Z24" si="17">+D5</f>
+        <f>+D5</f>
         <v>657</v>
       </c>
       <c r="E24" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="E24:Z24" si="17">+E5</f>
         <v>612</v>
       </c>
       <c r="F24" s="22">
@@ -12001,11 +12001,11 @@
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="22">
-        <f t="shared" ref="D25:Z25" si="19">+D4</f>
+        <f>+D4</f>
         <v>860</v>
       </c>
       <c r="E25" s="22">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="E25:Z25" si="19">+E4</f>
         <v>874</v>
       </c>
       <c r="F25" s="22">
@@ -30521,11 +30521,11 @@
         <v>36</v>
       </c>
       <c r="B25" s="14">
-        <f t="shared" ref="B25:AA25" si="17">SUM(B14+B4)/2</f>
+        <f>SUM(B14+B4)/2</f>
         <v>188.15</v>
       </c>
       <c r="C25" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="C25:AA25" si="17">SUM(C14+C4)/2</f>
         <v>195.2</v>
       </c>
       <c r="D25" s="14">
@@ -32790,11 +32790,11 @@
         <v>35</v>
       </c>
       <c r="B24" s="14">
-        <f t="shared" ref="B24:Z24" si="10">(B14+B5+B5)/3</f>
+        <f>(B14+B5+B5)/3</f>
         <v>233.9</v>
       </c>
       <c r="C24" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="C24:Z24" si="10">(C14+C5+C5)/3</f>
         <v>249.63333333333333</v>
       </c>
       <c r="D24" s="14">
@@ -32899,11 +32899,11 @@
         <v>36</v>
       </c>
       <c r="B25" s="14">
-        <f t="shared" ref="B25:Z25" si="11">SUM(B14+B4+B4)/3</f>
+        <f>SUM(B14+B4+B4)/3</f>
         <v>249.10000000000002</v>
       </c>
       <c r="C25" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="C25:Z25" si="11">SUM(C14+C4+C4)/3</f>
         <v>254.5</v>
       </c>
       <c r="D25" s="14">
@@ -38452,67 +38452,67 @@
       <c r="J22" s="14"/>
       <c r="K22" s="14"/>
       <c r="L22" s="15">
-        <f t="shared" ref="L22" si="14">SUM(L2+L3+L5+L6+L7+L8+L9+L10+L11+L12+L13)/11</f>
+        <f>SUM(L2+L3+L5+L6+L7+L8+L9+L10+L11+L12+L13)/11</f>
         <v>2519.2727272727275</v>
       </c>
       <c r="M22" s="15">
-        <f t="shared" ref="M22:AA22" si="15">SUM(M2+M3+M5+M6+M7+M8+M9+M10+M11+M12+M13)/11</f>
+        <f t="shared" ref="M22:AA22" si="14">SUM(M2+M3+M5+M6+M7+M8+M9+M10+M11+M12+M13)/11</f>
         <v>2519.2727272727275</v>
       </c>
       <c r="N22" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2350.6363636363635</v>
       </c>
       <c r="O22" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2355.181818181818</v>
       </c>
       <c r="P22" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2442.2727272727275</v>
       </c>
       <c r="Q22" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2395.4545454545455</v>
       </c>
       <c r="R22" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2479.4545454545455</v>
       </c>
       <c r="S22" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2348.2727272727275</v>
       </c>
       <c r="T22" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2282.5454545454545</v>
       </c>
       <c r="U22" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2259.181818181818</v>
       </c>
       <c r="V22" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2491.4545454545455</v>
       </c>
       <c r="W22" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2609.4545454545455</v>
       </c>
       <c r="X22" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2434.818181818182</v>
       </c>
       <c r="Y22" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2165.909090909091</v>
       </c>
       <c r="Z22" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2332.4545454545455</v>
       </c>
       <c r="AA22" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2332.4545454545455</v>
       </c>
     </row>
@@ -38531,67 +38531,67 @@
       <c r="J23" s="28"/>
       <c r="K23" s="28"/>
       <c r="L23" s="22">
-        <f t="shared" ref="L23" si="16">(L4+L5)/2</f>
+        <f t="shared" ref="L23" si="15">(L4+L5)/2</f>
         <v>855.5</v>
       </c>
       <c r="M23" s="22">
-        <f t="shared" ref="M23:AA23" si="17">(M4+M5)/2</f>
+        <f t="shared" ref="M23:AA23" si="16">(M4+M5)/2</f>
         <v>855.5</v>
       </c>
       <c r="N23" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>855</v>
       </c>
       <c r="O23" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>850</v>
       </c>
       <c r="P23" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>857.5</v>
       </c>
       <c r="Q23" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>821.5</v>
       </c>
       <c r="R23" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>834.5</v>
       </c>
       <c r="S23" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>842</v>
       </c>
       <c r="T23" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>836</v>
       </c>
       <c r="U23" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>862</v>
       </c>
       <c r="V23" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>926.5</v>
       </c>
       <c r="W23" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>959.5</v>
       </c>
       <c r="X23" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>891</v>
       </c>
       <c r="Y23" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>851</v>
       </c>
       <c r="Z23" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>867</v>
       </c>
       <c r="AA23" s="22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>867</v>
       </c>
     </row>
@@ -38610,68 +38610,68 @@
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
       <c r="L24" s="15">
-        <f t="shared" ref="L24" si="18">(L14+L5+L5)/3</f>
-        <v>1367.3333333333333</v>
+        <f>SUM(L14-L4)</f>
+        <v>1601</v>
       </c>
       <c r="M24" s="15">
-        <f t="shared" ref="M24:AA24" si="19">(M14+M5+M5)/3</f>
-        <v>1367.3333333333333</v>
+        <f t="shared" ref="M24:AA24" si="17">SUM(M14-M4)</f>
+        <v>1601</v>
       </c>
       <c r="N24" s="15">
-        <f t="shared" si="19"/>
-        <v>1342</v>
+        <f t="shared" si="17"/>
+        <v>1538</v>
       </c>
       <c r="O24" s="15">
-        <f t="shared" si="19"/>
-        <v>1305.3333333333333</v>
+        <f t="shared" si="17"/>
+        <v>1490</v>
       </c>
       <c r="P24" s="15">
-        <f t="shared" si="19"/>
-        <v>1393.3333333333333</v>
+        <f t="shared" si="17"/>
+        <v>1625</v>
       </c>
       <c r="Q24" s="15">
-        <f t="shared" si="19"/>
-        <v>1308.3333333333333</v>
+        <f t="shared" si="17"/>
+        <v>1523</v>
       </c>
       <c r="R24" s="15">
-        <f t="shared" si="19"/>
-        <v>1382.6666666666667</v>
+        <f t="shared" si="17"/>
+        <v>1639</v>
       </c>
       <c r="S24" s="15">
-        <f t="shared" si="19"/>
-        <v>1350.3333333333333</v>
+        <f t="shared" si="17"/>
+        <v>1561</v>
       </c>
       <c r="T24" s="15">
-        <f t="shared" si="19"/>
-        <v>1312</v>
+        <f t="shared" si="17"/>
+        <v>1506</v>
       </c>
       <c r="U24" s="15">
-        <f t="shared" si="19"/>
-        <v>1371.3333333333333</v>
+        <f t="shared" si="17"/>
+        <v>1572</v>
       </c>
       <c r="V24" s="15">
-        <f t="shared" si="19"/>
-        <v>1484</v>
+        <f t="shared" si="17"/>
+        <v>1714</v>
       </c>
       <c r="W24" s="15">
-        <f t="shared" si="19"/>
-        <v>1548.3333333333333</v>
+        <f t="shared" si="17"/>
+        <v>1802</v>
       </c>
       <c r="X24" s="15">
-        <f t="shared" si="19"/>
-        <v>1417</v>
+        <f t="shared" si="17"/>
+        <v>1626</v>
       </c>
       <c r="Y24" s="15">
-        <f t="shared" si="19"/>
-        <v>1329.6666666666667</v>
+        <f t="shared" si="17"/>
+        <v>1504</v>
       </c>
       <c r="Z24" s="15">
-        <f t="shared" si="19"/>
-        <v>1369.3333333333333</v>
+        <f t="shared" si="17"/>
+        <v>1581</v>
       </c>
       <c r="AA24" s="15">
-        <f t="shared" si="19"/>
-        <v>1369.3333333333333</v>
+        <f t="shared" si="17"/>
+        <v>1581</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
@@ -38689,68 +38689,68 @@
       <c r="J25" s="14"/>
       <c r="K25" s="14"/>
       <c r="L25" s="15">
-        <f t="shared" ref="L25" si="20">SUM(L14+L4+L4)/3</f>
-        <v>1454.6666666666667</v>
+        <f>SUM(L14-L5)</f>
+        <v>1732</v>
       </c>
       <c r="M25" s="15">
-        <f t="shared" ref="M25:AA25" si="21">SUM(M14+M4+M4)/3</f>
-        <v>1454.6666666666667</v>
+        <f t="shared" ref="M25:AA25" si="18">SUM(M14-M5)</f>
+        <v>1732</v>
       </c>
       <c r="N25" s="15">
-        <f t="shared" si="21"/>
-        <v>1444.6666666666667</v>
+        <f t="shared" si="18"/>
+        <v>1692</v>
       </c>
       <c r="O25" s="15">
-        <f t="shared" si="21"/>
-        <v>1470.6666666666667</v>
+        <f t="shared" si="18"/>
+        <v>1738</v>
       </c>
       <c r="P25" s="15">
-        <f t="shared" si="21"/>
-        <v>1416.6666666666667</v>
+        <f t="shared" si="18"/>
+        <v>1660</v>
       </c>
       <c r="Q25" s="15">
-        <f t="shared" si="21"/>
-        <v>1391.6666666666667</v>
+        <f t="shared" si="18"/>
+        <v>1648</v>
       </c>
       <c r="R25" s="15">
-        <f t="shared" si="21"/>
-        <v>1375.3333333333333</v>
+        <f t="shared" si="18"/>
+        <v>1628</v>
       </c>
       <c r="S25" s="15">
-        <f t="shared" si="21"/>
-        <v>1398.3333333333333</v>
+        <f t="shared" si="18"/>
+        <v>1633</v>
       </c>
       <c r="T25" s="15">
-        <f t="shared" si="21"/>
-        <v>1416</v>
+        <f t="shared" si="18"/>
+        <v>1662</v>
       </c>
       <c r="U25" s="15">
-        <f t="shared" si="21"/>
-        <v>1430</v>
+        <f t="shared" si="18"/>
+        <v>1660</v>
       </c>
       <c r="V25" s="15">
-        <f t="shared" si="21"/>
-        <v>1539.3333333333333</v>
+        <f t="shared" si="18"/>
+        <v>1797</v>
       </c>
       <c r="W25" s="15">
-        <f t="shared" si="21"/>
-        <v>1595.6666666666667</v>
+        <f t="shared" si="18"/>
+        <v>1873</v>
       </c>
       <c r="X25" s="15">
-        <f t="shared" si="21"/>
-        <v>1481</v>
+        <f t="shared" si="18"/>
+        <v>1722</v>
       </c>
       <c r="Y25" s="15">
-        <f t="shared" si="21"/>
-        <v>1420.3333333333333</v>
+        <f t="shared" si="18"/>
+        <v>1640</v>
       </c>
       <c r="Z25" s="15">
-        <f t="shared" si="21"/>
-        <v>1468</v>
+        <f t="shared" si="18"/>
+        <v>1729</v>
       </c>
       <c r="AA25" s="15">
-        <f t="shared" si="21"/>
-        <v>1468</v>
+        <f t="shared" si="18"/>
+        <v>1729</v>
       </c>
     </row>
   </sheetData>
@@ -43254,108 +43254,108 @@
         <v>35</v>
       </c>
       <c r="B24" s="15">
-        <f t="shared" ref="B24:AA24" si="9">(B14+B5+B5)/3</f>
-        <v>108242</v>
+        <f>+B14-B4</f>
+        <v>135528</v>
       </c>
       <c r="C24" s="15">
-        <f t="shared" si="9"/>
-        <v>108626.33333333333</v>
+        <f t="shared" ref="C24:Z24" si="9">+C14-C4</f>
+        <v>135768</v>
       </c>
       <c r="D24" s="15">
         <f t="shared" si="9"/>
-        <v>108677</v>
+        <v>135781</v>
       </c>
       <c r="E24" s="15">
         <f t="shared" si="9"/>
-        <v>109496.33333333333</v>
+        <v>136293</v>
       </c>
       <c r="F24" s="15">
         <f t="shared" si="9"/>
-        <v>109989</v>
+        <v>136698</v>
       </c>
       <c r="G24" s="15">
         <f t="shared" si="9"/>
-        <v>110522.33333333333</v>
+        <v>137136</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="9"/>
-        <v>111104.66666666667</v>
+        <v>137641</v>
       </c>
       <c r="I24" s="15">
         <f t="shared" si="9"/>
-        <v>111955</v>
+        <v>138363</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="9"/>
-        <v>112618.33333333333</v>
+        <v>138886</v>
       </c>
       <c r="K24" s="15">
         <f t="shared" si="9"/>
-        <v>113005</v>
+        <v>139164</v>
       </c>
       <c r="L24" s="15">
         <f t="shared" si="9"/>
-        <v>113460.33333333333</v>
+        <v>139500</v>
       </c>
       <c r="M24" s="15">
         <f t="shared" si="9"/>
-        <v>113785</v>
+        <v>139773</v>
       </c>
       <c r="N24" s="15">
         <f t="shared" si="9"/>
-        <v>114219.66666666667</v>
+        <v>140168</v>
       </c>
       <c r="O24" s="15">
         <f t="shared" si="9"/>
-        <v>114555.66666666667</v>
+        <v>140365</v>
       </c>
       <c r="P24" s="15">
         <f t="shared" si="9"/>
-        <v>115567.66666666667</v>
+        <v>141208</v>
       </c>
       <c r="Q24" s="15">
         <f t="shared" si="9"/>
-        <v>117168.33333333333</v>
+        <v>142624</v>
       </c>
       <c r="R24" s="15">
         <f t="shared" si="9"/>
-        <v>118634</v>
+        <v>144356</v>
       </c>
       <c r="S24" s="15">
         <f t="shared" si="9"/>
-        <v>120266</v>
+        <v>145681</v>
       </c>
       <c r="T24" s="15">
         <f t="shared" si="9"/>
-        <v>121926.66666666667</v>
+        <v>147105</v>
       </c>
       <c r="U24" s="15">
         <f t="shared" si="9"/>
-        <v>123367.66666666667</v>
+        <v>148361</v>
       </c>
       <c r="V24" s="15">
         <f t="shared" si="9"/>
-        <v>124727.66666666667</v>
+        <v>149603</v>
       </c>
       <c r="W24" s="15">
         <f t="shared" si="9"/>
-        <v>126340.66666666667</v>
+        <v>151135</v>
       </c>
       <c r="X24" s="15">
         <f t="shared" si="9"/>
-        <v>127490.33333333333</v>
+        <v>152189</v>
       </c>
       <c r="Y24" s="15">
         <f t="shared" si="9"/>
-        <v>129057.33333333333</v>
+        <v>153716</v>
       </c>
       <c r="Z24" s="15">
         <f t="shared" si="9"/>
-        <v>130301</v>
+        <v>154856</v>
       </c>
       <c r="AA24" s="15">
-        <f t="shared" si="9"/>
-        <v>130301</v>
+        <f>+AA14-AA4</f>
+        <v>154856</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
@@ -43363,108 +43363,108 @@
         <v>36</v>
       </c>
       <c r="B25" s="15">
-        <f t="shared" ref="B25:AA25" si="10">SUM(B14+B4+B4)/3</f>
-        <v>111062</v>
+        <f>+B14-B5</f>
+        <v>139758</v>
       </c>
       <c r="C25" s="15">
-        <f t="shared" si="10"/>
-        <v>111491</v>
+        <f t="shared" ref="C25:AA25" si="10">+C14-C5</f>
+        <v>140065</v>
       </c>
       <c r="D25" s="15">
         <f t="shared" si="10"/>
-        <v>111896.33333333333</v>
+        <v>140610</v>
       </c>
       <c r="E25" s="15">
         <f t="shared" si="10"/>
-        <v>113245</v>
+        <v>141916</v>
       </c>
       <c r="F25" s="15">
         <f t="shared" si="10"/>
-        <v>113987</v>
+        <v>142695</v>
       </c>
       <c r="G25" s="15">
         <f t="shared" si="10"/>
-        <v>114651</v>
+        <v>143329</v>
       </c>
       <c r="H25" s="15">
         <f t="shared" si="10"/>
-        <v>115431.33333333333</v>
+        <v>144131</v>
       </c>
       <c r="I25" s="15">
         <f t="shared" si="10"/>
-        <v>116447</v>
+        <v>145101</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="10"/>
-        <v>117466.33333333333</v>
+        <v>146158</v>
       </c>
       <c r="K25" s="15">
         <f t="shared" si="10"/>
-        <v>118111</v>
+        <v>146823</v>
       </c>
       <c r="L25" s="15">
         <f t="shared" si="10"/>
-        <v>118751</v>
+        <v>147436</v>
       </c>
       <c r="M25" s="15">
         <f t="shared" si="10"/>
-        <v>119309</v>
+        <v>148059</v>
       </c>
       <c r="N25" s="15">
         <f t="shared" si="10"/>
-        <v>119961.66666666667</v>
+        <v>148781</v>
       </c>
       <c r="O25" s="15">
         <f t="shared" si="10"/>
-        <v>120552.33333333333</v>
+        <v>149360</v>
       </c>
       <c r="P25" s="15">
         <f t="shared" si="10"/>
-        <v>121912.33333333333</v>
+        <v>150725</v>
       </c>
       <c r="Q25" s="15">
         <f t="shared" si="10"/>
-        <v>123566.33333333333</v>
+        <v>152221</v>
       </c>
       <c r="R25" s="15">
         <f t="shared" si="10"/>
-        <v>125234.66666666667</v>
+        <v>154257</v>
       </c>
       <c r="S25" s="15">
         <f t="shared" si="10"/>
-        <v>127975.33333333333</v>
+        <v>157245</v>
       </c>
       <c r="T25" s="15">
         <f t="shared" si="10"/>
-        <v>130000</v>
+        <v>159215</v>
       </c>
       <c r="U25" s="15">
         <f t="shared" si="10"/>
-        <v>131745.66666666666</v>
+        <v>160928</v>
       </c>
       <c r="V25" s="15">
         <f t="shared" si="10"/>
-        <v>133549.66666666666</v>
+        <v>162836</v>
       </c>
       <c r="W25" s="15">
         <f t="shared" si="10"/>
-        <v>135377.33333333334</v>
+        <v>164690</v>
       </c>
       <c r="X25" s="15">
         <f t="shared" si="10"/>
-        <v>136739.66666666666</v>
+        <v>166063</v>
       </c>
       <c r="Y25" s="15">
         <f t="shared" si="10"/>
-        <v>137944.66666666666</v>
+        <v>167047</v>
       </c>
       <c r="Z25" s="15">
         <f t="shared" si="10"/>
-        <v>139293.66666666666</v>
+        <v>168345</v>
       </c>
       <c r="AA25" s="15">
         <f t="shared" si="10"/>
-        <v>139293.66666666666</v>
+        <v>168345</v>
       </c>
     </row>
   </sheetData>
@@ -52754,7 +52754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E1FDDC4-39F1-4EAD-A074-F82B2A2216D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58C4EB15-4DAE-4825-822B-BDC6D79F30CE}">
   <dimension ref="A1:AA25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -52926,7 +52926,6 @@
         <v>357178</v>
       </c>
       <c r="AA2" s="5">
-        <f>+Z2</f>
         <v>357178</v>
       </c>
     </row>
@@ -53010,7 +53009,6 @@
         <v>25066</v>
       </c>
       <c r="AA3" s="5">
-        <f t="shared" ref="AA3:AA25" si="0">+Z3</f>
         <v>25066</v>
       </c>
     </row>
@@ -53094,7 +53092,6 @@
         <v>23190</v>
       </c>
       <c r="AA4" s="5">
-        <f t="shared" si="0"/>
         <v>23190</v>
       </c>
     </row>
@@ -53178,7 +53175,6 @@
         <v>14073</v>
       </c>
       <c r="AA5" s="5">
-        <f t="shared" si="0"/>
         <v>14073</v>
       </c>
     </row>
@@ -53262,7 +53258,6 @@
         <v>16456</v>
       </c>
       <c r="AA6" s="5">
-        <f t="shared" si="0"/>
         <v>16456</v>
       </c>
     </row>
@@ -53346,7 +53341,6 @@
         <v>82903</v>
       </c>
       <c r="AA7" s="5">
-        <f t="shared" si="0"/>
         <v>82903</v>
       </c>
     </row>
@@ -53430,7 +53424,6 @@
         <v>43571</v>
       </c>
       <c r="AA8" s="5">
-        <f t="shared" si="0"/>
         <v>43571</v>
       </c>
     </row>
@@ -53514,7 +53507,6 @@
         <v>28426</v>
       </c>
       <c r="AA9" s="5">
-        <f t="shared" si="0"/>
         <v>28426</v>
       </c>
     </row>
@@ -53598,7 +53590,6 @@
         <v>133894</v>
       </c>
       <c r="AA10" s="5">
-        <f t="shared" si="0"/>
         <v>133894</v>
       </c>
     </row>
@@ -53682,7 +53673,6 @@
         <v>22012</v>
       </c>
       <c r="AA11" s="5">
-        <f t="shared" si="0"/>
         <v>22012</v>
       </c>
     </row>
@@ -53766,7 +53756,6 @@
         <v>17623</v>
       </c>
       <c r="AA12" s="5">
-        <f t="shared" si="0"/>
         <v>17623</v>
       </c>
     </row>
@@ -53850,7 +53839,6 @@
         <v>9081</v>
       </c>
       <c r="AA13" s="5">
-        <f t="shared" si="0"/>
         <v>9081</v>
       </c>
     </row>
@@ -53931,11 +53919,9 @@
         <v>11681</v>
       </c>
       <c r="Z14" s="5">
-        <f>+Y14</f>
         <v>11681</v>
       </c>
       <c r="AA14" s="5">
-        <f t="shared" si="0"/>
         <v>11681</v>
       </c>
     </row>
@@ -53979,103 +53965,103 @@
         <v>503126</v>
       </c>
       <c r="C16" s="22">
-        <f t="shared" ref="C16:Z16" si="1">SUM(C2:C13)</f>
+        <f t="shared" ref="C16:Z16" si="0">SUM(C2:C13)</f>
         <v>504645</v>
       </c>
       <c r="D16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>510571</v>
       </c>
       <c r="E16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>498463</v>
       </c>
       <c r="F16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>510830</v>
       </c>
       <c r="G16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>524845</v>
       </c>
       <c r="H16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>535651</v>
       </c>
       <c r="I16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>560470</v>
       </c>
       <c r="J16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>571068</v>
       </c>
       <c r="K16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>564431</v>
       </c>
       <c r="L16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>582858</v>
       </c>
       <c r="M16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>593909</v>
       </c>
       <c r="N16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>607547</v>
       </c>
       <c r="O16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>617631</v>
       </c>
       <c r="P16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>627615</v>
       </c>
       <c r="Q16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>644326</v>
       </c>
       <c r="R16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>664223</v>
       </c>
       <c r="S16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>680730</v>
       </c>
       <c r="T16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>693336</v>
       </c>
       <c r="U16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>704180</v>
       </c>
       <c r="V16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>695685</v>
       </c>
       <c r="W16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>733817</v>
       </c>
       <c r="X16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>770064</v>
       </c>
       <c r="Y16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>774324</v>
       </c>
       <c r="Z16" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>773473</v>
       </c>
       <c r="AA16" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AA16:AA25" si="1">+Z16</f>
         <v>773473</v>
       </c>
     </row>
@@ -54184,7 +54170,7 @@
         <v>573975</v>
       </c>
       <c r="AA17" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>573975</v>
       </c>
     </row>
@@ -54293,7 +54279,7 @@
         <v>599041</v>
       </c>
       <c r="AA18" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>599041</v>
       </c>
     </row>
@@ -54402,7 +54388,7 @@
         <v>174432</v>
       </c>
       <c r="AA19" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>174432</v>
       </c>
     </row>
@@ -54511,7 +54497,7 @@
         <v>137169</v>
       </c>
       <c r="AA20" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>137169</v>
       </c>
     </row>
@@ -54620,7 +54606,7 @@
         <v>151242</v>
       </c>
       <c r="AA21" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>151242</v>
       </c>
     </row>
@@ -54838,7 +54824,7 @@
         <v>37263</v>
       </c>
       <c r="AA23" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>37263</v>
       </c>
     </row>
@@ -54947,7 +54933,7 @@
         <v>-11509</v>
       </c>
       <c r="AA24" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-11509</v>
       </c>
     </row>
@@ -55056,7 +55042,7 @@
         <v>-2392</v>
       </c>
       <c r="AA25" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-2392</v>
       </c>
     </row>
@@ -57160,11 +57146,11 @@
         <v>35</v>
       </c>
       <c r="B24" s="22">
-        <f t="shared" ref="B24:Z24" si="11">SUM(B14-B4)</f>
+        <f>SUM(B14-B4)</f>
         <v>2319</v>
       </c>
       <c r="C24" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="B24:Z24" si="11">SUM(C14-C4)</f>
         <v>2536</v>
       </c>
       <c r="D24" s="22">
